--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92550160722</v>
+        <v>46157.93101041132</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93101041132</v>
+        <v>46157.93128592102</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93128592102</v>
+        <v>46157.93377098555</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93377098555</v>
+        <v>46157.93686006359</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93686006359</v>
+        <v>46158.28201714253</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28201714253</v>
+        <v>46158.29730542514</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29730542514</v>
+        <v>46158.29798724064</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29798724064</v>
+        <v>46158.33364214756</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33364214756</v>
+        <v>46158.37216550051</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37216550051</v>
+        <v>46158.37272266581</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
